--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-08-2025.xlsx
@@ -591,27 +591,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£12.62</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -712,27 +712,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -805,7 +805,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£16.18</t>
+          <t>£15.74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -833,27 +833,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -926,7 +926,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£16.40</t>
+          <t>£15.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -954,27 +954,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£21.08</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1075,27 +1075,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£22.76</t>
+          <t>£22.23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1196,27 +1196,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>£22.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1317,27 +1317,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£26.35</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1438,27 +1438,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£28.75</t>
+          <t>£27.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1559,27 +1559,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£27.49</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1680,27 +1680,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>£36.50</t>
+          <t>£36.30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1801,27 +1801,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£34.75</t>
+          <t>£33.99</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1922,27 +1922,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2043,27 +2043,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£41.92</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2164,27 +2164,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£43.20</t>
+          <t>£41.85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2285,27 +2285,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£750.0</t>
+          <t>£719.88</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>£960.0</t>
+          <t>£935.88</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2503,27 +2503,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£29.75</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2624,27 +2624,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -2745,27 +2745,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£40.50</t>
+          <t>£39.15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2866,27 +2866,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£44.99</t>
+          <t>£43.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2987,27 +2987,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>£45.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3108,27 +3108,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£43.90</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3229,27 +3229,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -3350,27 +3350,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3471,27 +3471,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.138); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7fe1c78d5+2802741]
-	GetHandleVerifier [0x0x7ff7fdf2eb70+79568]
-	(No symbol) [0x0x7ff7fdccc0fa]
-	(No symbol) [0x0x7ff7fdd22a96]
-	(No symbol) [0x0x7ff7fdd22d4c]
-	(No symbol) [0x0x7ff7fdd76017]
-	(No symbol) [0x0x7ff7fdd4accf]
-	(No symbol) [0x0x7ff7fdd72e24]
-	(No symbol) [0x0x7ff7fdd4aa63]
-	(No symbol) [0x0x7ff7fdd13c91]
-	(No symbol) [0x0x7ff7fdd14a23]
-	GetHandleVerifier [0x0x7ff7fe1f2ced+2979917]
-	GetHandleVerifier [0x0x7ff7fe1ed0f3+2956371]
-	GetHandleVerifier [0x0x7ff7fe20acbd+3078173]
-	GetHandleVerifier [0x0x7ff7fdf4836e+184014]
-	GetHandleVerifier [0x0x7ff7fdf5024f+216495]
-	GetHandleVerifier [0x0x7ff7fdf370c4+113700]
-	GetHandleVerifier [0x0x7ff7fdf37279+114137]
-	GetHandleVerifier [0x0x7ff7fdf1df78+10968]
-	BaseThreadInitThunk [0x0x7ff8a9f0e8d7+23]
-	RtlUserThreadStart [0x0x7ff8ab1bc34c+44]
+	GetHandleVerifier [0x0x7ff6d52b78d5+2802741]
+	GetHandleVerifier [0x0x7ff6d501eb70+79568]
+	(No symbol) [0x0x7ff6d4dbc0fa]
+	(No symbol) [0x0x7ff6d4e12a96]
+	(No symbol) [0x0x7ff6d4e12d4c]
+	(No symbol) [0x0x7ff6d4e66017]
+	(No symbol) [0x0x7ff6d4e3accf]
+	(No symbol) [0x0x7ff6d4e62e24]
+	(No symbol) [0x0x7ff6d4e3aa63]
+	(No symbol) [0x0x7ff6d4e03c91]
+	(No symbol) [0x0x7ff6d4e04a23]
+	GetHandleVerifier [0x0x7ff6d52e2ced+2979917]
+	GetHandleVerifier [0x0x7ff6d52dd0f3+2956371]
+	GetHandleVerifier [0x0x7ff6d52facbd+3078173]
+	GetHandleVerifier [0x0x7ff6d503836e+184014]
+	GetHandleVerifier [0x0x7ff6d504024f+216495]
+	GetHandleVerifier [0x0x7ff6d50270c4+113700]
+	GetHandleVerifier [0x0x7ff6d5027279+114137]
+	GetHandleVerifier [0x0x7ff6d500df78+10968]
+	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
+	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
         </is>
       </c>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>£1249.6</t>
+          <t>£1152.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>£1375.2</t>
+          <t>£1280.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>£1358.4</t>
+          <t>£1280.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
